--- a/Estoque/Items.xlsx
+++ b/Estoque/Items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,19 @@
         <v>90</v>
       </c>
       <c r="C4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Azeites</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
         <v>3</v>
       </c>
     </row>
